--- a/data/department_schedules_midterms/Çevre Mühendisliği.xlsx
+++ b/data/department_schedules_midterms/Çevre Mühendisliği.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_midterms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C9186F-3980-4AD4-B463-91E8494E9D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634F2DD7-5349-4966-BB5E-131423DDD7B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="22200" windowHeight="13700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4000" yWindow="2900" windowWidth="22200" windowHeight="10880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Year:</t>
   </si>
@@ -28,9 +28,6 @@
     <t>Course ID</t>
   </si>
   <si>
-    <t>Course Name</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -113,84 +110,6 @@
   </si>
   <si>
     <t>ÇEV 440</t>
-  </si>
-  <si>
-    <t>Analytical Chemistry</t>
-  </si>
-  <si>
-    <t>Computer Programming</t>
-  </si>
-  <si>
-    <t>Çevre Ekolojisi</t>
-  </si>
-  <si>
-    <t>Kariyer Planlama</t>
-  </si>
-  <si>
-    <t>Mathematics II</t>
-  </si>
-  <si>
-    <t>Physics II</t>
-  </si>
-  <si>
-    <t>Statik ve Mukavemet</t>
-  </si>
-  <si>
-    <t>Technical English II</t>
-  </si>
-  <si>
-    <t>Bilgisayar Destekli Çizim</t>
-  </si>
-  <si>
-    <t>Environmental Chemistry Laboratory</t>
-  </si>
-  <si>
-    <t>Hidrolik</t>
-  </si>
-  <si>
-    <t>Hydrology</t>
-  </si>
-  <si>
-    <t>Mühendislikte İstatistik</t>
-  </si>
-  <si>
-    <t>Sayısal Analiz</t>
-  </si>
-  <si>
-    <t>Termodinamik</t>
-  </si>
-  <si>
-    <t>Atıksuların Uzaklaştırılması</t>
-  </si>
-  <si>
-    <t>Bioconversion of Wastes</t>
-  </si>
-  <si>
-    <t>Biyolojik Prosesler</t>
-  </si>
-  <si>
-    <t>Çevre ve Halk Sağlığı</t>
-  </si>
-  <si>
-    <t>Fundamentals of Air Pollution</t>
-  </si>
-  <si>
-    <t>Water Treatment</t>
-  </si>
-  <si>
-    <t>Arıtma Çamurlarının Kontrolü</t>
-  </si>
-  <si>
-    <t>Atıksu Arıtma Tesisleri Tasarımı</t>
-  </si>
-  <si>
-    <t>Desalinasyon Teknolojileri</t>
-  </si>
-  <si>
-    <t>Endüstriyel Atıksuların Arıtımı</t>
-  </si>
-  <si>
-    <t>İş Sağlığı ve Güvenliği</t>
   </si>
 </sst>
 </file>
@@ -298,10 +217,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -374,12 +290,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{721AB193-2C3B-4687-B23B-09E144B0A7D1}" name="Table1" displayName="Table1" ref="A1:E27" totalsRowShown="0" headerRowDxfId="8" dataDxfId="6" headerRowBorderDxfId="7" tableBorderDxfId="5">
-  <autoFilter ref="A1:E27" xr:uid="{721AB193-2C3B-4687-B23B-09E144B0A7D1}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{C391A304-A814-4BC2-8528-DBD24EA253A1}" name="Year:" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{D00A80C7-5BC5-4BB0-945D-AB15F4381E48}" name="Course ID" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{E771576C-82A1-4278-A23C-77775F9FB313}" name="Course Name" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{721AB193-2C3B-4687-B23B-09E144B0A7D1}" name="Table1" displayName="Table1" ref="A1:D27" totalsRowShown="0" headerRowDxfId="7" dataDxfId="5" headerRowBorderDxfId="6" tableBorderDxfId="4">
+  <autoFilter ref="A1:D27" xr:uid="{721AB193-2C3B-4687-B23B-09E144B0A7D1}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{C391A304-A814-4BC2-8528-DBD24EA253A1}" name="Year:" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{D00A80C7-5BC5-4BB0-945D-AB15F4381E48}" name="Course ID" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{1634D8BA-3484-4A97-B955-16862F1DC12D}" name="Date" dataDxfId="1"/>
     <tableColumn id="6" xr3:uid="{B1A4B95E-CF35-4FFC-BD0A-F0C7EDC6B4ED}" name="Rooms" dataDxfId="0"/>
   </tableColumns>
@@ -674,15 +589,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.90625" customWidth="1"/>
-    <col min="3" max="3" width="32.54296875" customWidth="1"/>
-    <col min="5" max="5" width="39" customWidth="1"/>
+    <col min="4" max="4" width="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -695,449 +609,368 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="D2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="2">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="2">
-        <v>5</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="2">
-        <v>4</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="2">
-        <v>1</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="2">
-        <v>2</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="2">
-        <v>2</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
-        <v>1</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
+        <v>2</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="2">
-        <v>3</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="3">
-        <v>2</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3">
+        <v>8</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="3">
+      <c r="C11" s="3">
+        <v>7</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>2</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="3">
+        <v>6</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
+        <v>2</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="3">
+        <v>9</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
+        <v>2</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="3">
         <v>8</v>
       </c>
-      <c r="E10" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="3">
-        <v>2</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="3">
-        <v>7</v>
-      </c>
-      <c r="E11" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="3">
-        <v>2</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="3">
-        <v>6</v>
-      </c>
-      <c r="E12" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="3">
-        <v>2</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="3">
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
+        <v>2</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="3">
         <v>9</v>
       </c>
-      <c r="E13" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="3">
-        <v>2</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="3">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="3">
-        <v>2</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="3">
+        <v>2</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="3">
-        <v>9</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="3">
-        <v>2</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>45</v>
+      <c r="C16" s="3">
+        <v>10</v>
       </c>
       <c r="D16" s="3">
-        <v>10</v>
-      </c>
-      <c r="E16" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
         <v>3</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>46</v>
+        <v>19</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
       </c>
-      <c r="E17" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
         <v>3</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>47</v>
+        <v>20</v>
+      </c>
+      <c r="C18" s="4">
+        <v>3</v>
       </c>
       <c r="D18" s="4">
-        <v>3</v>
-      </c>
-      <c r="E18" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
         <v>3</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>48</v>
+        <v>21</v>
+      </c>
+      <c r="C19" s="4">
+        <v>5</v>
       </c>
       <c r="D19" s="4">
-        <v>5</v>
-      </c>
-      <c r="E19" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
         <v>3</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>49</v>
+        <v>22</v>
+      </c>
+      <c r="C20" s="4">
+        <v>2</v>
       </c>
       <c r="D20" s="4">
-        <v>2</v>
-      </c>
-      <c r="E20" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
         <v>3</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>50</v>
+        <v>23</v>
+      </c>
+      <c r="C21" s="4">
+        <v>4</v>
       </c>
       <c r="D21" s="4">
-        <v>4</v>
-      </c>
-      <c r="E21" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
         <v>3</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>51</v>
+        <v>24</v>
+      </c>
+      <c r="C22" s="4">
+        <v>2</v>
       </c>
       <c r="D22" s="4">
-        <v>2</v>
-      </c>
-      <c r="E22" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>4</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>52</v>
+        <v>25</v>
+      </c>
+      <c r="C23" s="5">
+        <v>10</v>
       </c>
       <c r="D23" s="5">
-        <v>10</v>
-      </c>
-      <c r="E23" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>4</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>53</v>
+        <v>26</v>
+      </c>
+      <c r="C24" s="5">
+        <v>9</v>
       </c>
       <c r="D24" s="5">
-        <v>9</v>
-      </c>
-      <c r="E24" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>4</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>54</v>
+        <v>27</v>
+      </c>
+      <c r="C25" s="5">
+        <v>6</v>
       </c>
       <c r="D25" s="5">
-        <v>6</v>
-      </c>
-      <c r="E25" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>4</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>55</v>
+        <v>28</v>
+      </c>
+      <c r="C26" s="5">
+        <v>7</v>
       </c>
       <c r="D26" s="5">
-        <v>7</v>
-      </c>
-      <c r="E26" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>4</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>56</v>
+        <v>29</v>
+      </c>
+      <c r="C27" s="5">
+        <v>8</v>
       </c>
       <c r="D27" s="5">
-        <v>8</v>
-      </c>
-      <c r="E27" s="5">
         <v>1</v>
       </c>
     </row>

--- a/data/department_schedules_midterms/Çevre Mühendisliği.xlsx
+++ b/data/department_schedules_midterms/Çevre Mühendisliği.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_midterms\modified\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/department_schedules_midterms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73EA8EB4-B532-4208-98EB-A12DAEDB9EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{73EA8EB4-B532-4208-98EB-A12DAEDB9EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BCEDE16-FF5A-4A4F-93C1-22CD91648D48}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17640" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="64">
   <si>
     <t>Year:</t>
   </si>
@@ -194,6 +194,24 @@
   </si>
   <si>
     <t>Rooms Used</t>
+  </si>
+  <si>
+    <t>C202</t>
+  </si>
+  <si>
+    <t>CAD1</t>
+  </si>
+  <si>
+    <t>Amfi 1</t>
+  </si>
+  <si>
+    <t>DZ01</t>
+  </si>
+  <si>
+    <t>C204</t>
+  </si>
+  <si>
+    <t>C201</t>
   </si>
 </sst>
 </file>
@@ -292,7 +310,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -316,6 +334,24 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="7">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -345,24 +381,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -377,14 +395,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6CCEB3C6-E865-4295-8FE4-F476D4D417BB}" name="Table1" displayName="Table1" ref="A1:F27" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6CCEB3C6-E865-4295-8FE4-F476D4D417BB}" name="Table1" displayName="Table1" ref="A1:F27" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A1:F27" xr:uid="{6CCEB3C6-E865-4295-8FE4-F476D4D417BB}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{C4437867-2534-4236-B6AB-5C3E485ACB49}" name="Year:" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{EADDAB49-7C50-4B3C-BFF5-E79F2400D882}" name="Course ID" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{F699FC73-49EC-4E47-879F-593C800FD533}" name="Date" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{77A316F6-1D1E-4587-A285-E742C9DD1DB5}" name="Rooms" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{6B7416AA-CF55-42CC-B83E-CB1D385E192C}" name="Course Name" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{C4437867-2534-4236-B6AB-5C3E485ACB49}" name="Year:" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{EADDAB49-7C50-4B3C-BFF5-E79F2400D882}" name="Course ID" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{F699FC73-49EC-4E47-879F-593C800FD533}" name="Date" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{77A316F6-1D1E-4587-A285-E742C9DD1DB5}" name="Rooms" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{6B7416AA-CF55-42CC-B83E-CB1D385E192C}" name="Course Name" dataDxfId="0"/>
     <tableColumn id="6" xr3:uid="{12B093FB-CE67-437D-A74D-B80C5470270A}" name="Rooms Used"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -679,14 +697,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="10.90625" customWidth="1"/>
-    <col min="5" max="5" width="44.90625" customWidth="1"/>
-    <col min="6" max="6" width="46.81640625" customWidth="1"/>
+    <col min="2" max="2" width="10.9296875" customWidth="1"/>
+    <col min="5" max="5" width="44.9296875" customWidth="1"/>
+    <col min="6" max="6" width="46.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -706,7 +724,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -722,9 +740,11 @@
       <c r="E2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F2" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -740,9 +760,11 @@
       <c r="E3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F3" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -758,9 +780,11 @@
       <c r="E4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F4" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -776,9 +800,11 @@
       <c r="E5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F5" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -794,9 +820,11 @@
       <c r="E6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F6" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -812,9 +840,11 @@
       <c r="E7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F7" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -830,9 +860,11 @@
       <c r="E8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F8" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
         <v>1</v>
       </c>
@@ -848,9 +880,11 @@
       <c r="E9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F9" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="5">
         <v>2</v>
       </c>
@@ -866,9 +900,11 @@
       <c r="E10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F10" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="5">
         <v>2</v>
       </c>
@@ -884,9 +920,11 @@
       <c r="E11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F11" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="5">
         <v>2</v>
       </c>
@@ -902,9 +940,11 @@
       <c r="E12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F12" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="5">
         <v>2</v>
       </c>
@@ -920,9 +960,11 @@
       <c r="E13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F13" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="5">
         <v>2</v>
       </c>
@@ -938,9 +980,11 @@
       <c r="E14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F14" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="5">
         <v>2</v>
       </c>
@@ -956,9 +1000,11 @@
       <c r="E15" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F15" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="5">
         <v>2</v>
       </c>
@@ -974,9 +1020,11 @@
       <c r="E16" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="6"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F16" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="7">
         <v>3</v>
       </c>
@@ -992,9 +1040,11 @@
       <c r="E17" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="8"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F17" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" s="7">
         <v>3</v>
       </c>
@@ -1010,9 +1060,11 @@
       <c r="E18" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="8"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F18" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" s="7">
         <v>3</v>
       </c>
@@ -1028,9 +1080,11 @@
       <c r="E19" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="8"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F19" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" s="7">
         <v>3</v>
       </c>
@@ -1046,9 +1100,11 @@
       <c r="E20" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F20" s="8"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F20" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="7">
         <v>3</v>
       </c>
@@ -1064,9 +1120,11 @@
       <c r="E21" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F21" s="8"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F21" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" s="7">
         <v>3</v>
       </c>
@@ -1082,9 +1140,11 @@
       <c r="E22" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F22" s="8"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F22" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" s="9">
         <v>4</v>
       </c>
@@ -1100,9 +1160,11 @@
       <c r="E23" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F23" s="10"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F23" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" s="9">
         <v>4</v>
       </c>
@@ -1118,9 +1180,11 @@
       <c r="E24" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F24" s="10"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F24" s="10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" s="9">
         <v>4</v>
       </c>
@@ -1136,9 +1200,11 @@
       <c r="E25" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F25" s="10"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F25" s="10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" s="9">
         <v>4</v>
       </c>
@@ -1154,9 +1220,11 @@
       <c r="E26" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F26" s="10"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F26" s="10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" s="9">
         <v>4</v>
       </c>
@@ -1172,7 +1240,9 @@
       <c r="E27" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F27" s="10"/>
+      <c r="F27" s="10" t="s">
+        <v>62</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/department_schedules_midterms/Çevre Mühendisliği.xlsx
+++ b/data/department_schedules_midterms/Çevre Mühendisliği.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/department_schedules_midterms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{73EA8EB4-B532-4208-98EB-A12DAEDB9EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BCEDE16-FF5A-4A4F-93C1-22CD91648D48}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{73EA8EB4-B532-4208-98EB-A12DAEDB9EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31FF252D-4158-414C-86CD-3F74195D6827}"/>
   <bookViews>
-    <workbookView xWindow="-17640" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-8910" yWindow="-13500" windowWidth="22080" windowHeight="9315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -202,9 +202,6 @@
     <t>CAD1</t>
   </si>
   <si>
-    <t>Amfi 1</t>
-  </si>
-  <si>
     <t>DZ01</t>
   </si>
   <si>
@@ -212,6 +209,9 @@
   </si>
   <si>
     <t>C201</t>
+  </si>
+  <si>
+    <t>Amfi 3</t>
   </si>
 </sst>
 </file>
@@ -801,7 +801,7 @@
         <v>34</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
@@ -821,7 +821,7 @@
         <v>35</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
@@ -921,7 +921,7 @@
         <v>40</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
@@ -1021,7 +1021,7 @@
         <v>45</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.45">
@@ -1041,7 +1041,7 @@
         <v>46</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.45">
@@ -1081,7 +1081,7 @@
         <v>48</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.45">
@@ -1101,7 +1101,7 @@
         <v>49</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.45">
@@ -1121,7 +1121,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.45">
@@ -1141,7 +1141,7 @@
         <v>51</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.45">
@@ -1181,7 +1181,7 @@
         <v>53</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.45">
@@ -1201,7 +1201,7 @@
         <v>54</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.45">
@@ -1221,7 +1221,7 @@
         <v>55</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.45">
@@ -1241,7 +1241,7 @@
         <v>56</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
